--- a/regulatory-compliance/cloud-foundation/9.1/eu-cra/vcf-91-companion-eu-cra.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/eu-cra/vcf-91-companion-eu-cra.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -1066,39 +1081,27 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in compliance measurement, scoring, and reporting capabilities that support an organization's conformity assessment activities. These tools allow operators to evaluate the state of their VCF environment against established security benchmarks and internal policies, producing quantitative results that can feed into broader compliance assessment programs. While conducting a full compliance program assessment is an organizational responsibility, VCF provides the technical instrumentation needed to assess and report on infrastructure conformity.
-VCF Operations includes a compliance scoring engine that measures how well objects in the environment conform to industrial, governmental, regulatory, or internal standards, including the DISA STIG. The compliance score is calculated as the ratio of compliant objects to the total number of objects assessed by a given benchmark, expressed as a percentage. When an object violates multiple standards, the compliance score reflects the most critical violation, so the worst-case posture is visible. The compliance score card displays 100 when all objects are compliant, and shows the count of non-compliant symptoms when violations exist. The Badge|Compliance metric provides a per-object compliance percentage based on triggered symptoms versus total symptoms. Compliance scores are calculated for all objects in the environment regardless of the viewing user's object-level permissions, so the assessment reflects the true state of the environment rather than a filtered view.
-VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Compliance alerts appear as violations to the standard, and the triggered symptoms appear as violated rules. The Compliance Alert List displays alerts that caused compliance violations in a sortable table, allowing administrators to prioritize remediation efforts. These alerts, combined with remediation guidance, help administrators move from assessment findings to corrective action.
-NSX provides a compliance report capability that allows administrators to compare their NSX networking configuration against IT policies and industry standards. This report identifies areas where the configuration deviates from the selected benchmark, supporting targeted remediation as part of an assessment cycle.
-At the VMware vCenter level, the Compliance interface compares the desired configuration state against the current state of each host in a cluster and calculates drift. The ClusterCompliance or HostCompliance object returned by the compliance check API contains the per-host compliance status, notifications, and check duration, and administrators can retrieve cluster compliance status through the REST API by calling the Compliance.get endpoint. This mechanism checks conformity with the cluster's configured desired state rather than with a regulatory benchmark directly, but when the desired state profile is built to match a regulatory baseline, the drift check supports ongoing assessment against that baseline.
-VCF's security configuration guidance, including the Security Configuration Guide and the DISA STIG, provides prescriptive baselines that organizations can use as the reference standard for their conformity assessments. VCF supports compliance measurement against guidelines for protecting controlled unclassified information. Administrators can automate assessment and remediation workflows through product interfaces, command-line tools, and APIs, reducing the manual effort involved in preparing for and responding to compliance assessments. VCF Operations also supports running workflows to remediate alerts or automate tasks, and maps out-of-the-box workflows to recommendations for automated remediation.
-These capabilities allow organizations to run repeatable, evidence-based conformity assessments against their VCF infrastructure, but the broader assessment program, including determining which laws, regulations, and contractual obligations apply, selecting assessment frameworks, scheduling assessment cycles, engaging independent auditors where required, and acting on assessment findings, remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to conformity assessments through Security Services Platform's Security Segmentation scoring and assessment capabilities, which provide measurable, evidence-based evaluation of an organization's network microsegmentation posture.
-Security Services Platform calculates a Security Segmentation Score on a 100-point weighted scale distributed across five categories. Points are awarded only when firewall rules and configuration meet specified requirements, giving compliance officers a quantitative metric to track microsegmentation maturity over time. The scoring system supports Relaxed mode, useful for gauging progress during segmentation implementation, and Strict mode, which applies stricter penalties for unidentified or unsegmented traffic for more stringent posture assessment. These modes allow organizations to choose the assessment rigor appropriate to their compliance posture.
-Environment Protection assessment evaluates whether workloads are protected by environment-specific segmentation policies, such as Dev, Prod, and Test. It measures the percentage of environment pairs operating in blocked mode and the percentage of all workloads covered by at least one environment rule, providing concrete metrics that can be presented during conformity assessments. The Security Segmentation Report includes an Inter-Environment Pair Protection Rule Action Summary section that provides a tabular summary of inter-environment communications, suitable for inclusion in audit evidence packages.
-The Security Segmentation Score Breakdown report provides more granular detail, listing total environments and pairs, protection rule action summaries, and identifying environment pairs that lack inter-environment policies. This breakdown allows auditors to pinpoint specific gaps in microsegmentation coverage rather than relying solely on the aggregate score.
-Rule Analysis, available within Security Services Platform, supports scheduled or on-demand analysis of the complete VMware vDefend (DFW) configuration. It detects contradictions where two rules have the same configuration with different actions, and identifies shadowed rules by comparing effective group memberships. Rule Analysis results can be exported as a CSV report for archival and review by external assessors. Role-based access control for Rule Analysis is enforced through Security Services Platform's platform roles; Enterprise Admin has full access to run, view, and download Rule Analysis reports. These capabilities help organizations demonstrate that their firewall policy is internally consistent and that analysis artifacts are available for auditor review.
-Security Intelligence, integrated within Security Services Platform in VMware vDefend, provides policy recommendations that can be reviewed, modified, and published to enforce network security policies. The View Impacted Flows capability displays unprotected traffic flows used to generate policy recommendations, giving auditors direct visibility into unprotected network paths.
-These vDefend capabilities address the network security dimension of conformity assessments. The broader compliance assessment program, including determining which regulations apply, selecting assessment frameworks, engaging assessors, and evaluating non-network controls, remains an organizational responsibility outside the scope of vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -1600,67 +1603,47 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>VCF provides configurable data retention controls within VCF Operations that allow administrators to align operational data retention periods with organizational requirements. These controls do not address the full scope of media and data retention governance, but they give administrators granular tuning over how long different categories of platform-generated data are kept.
-VCF Operations exposes data retention settings through Administration &gt; Global Settings &gt; Data Retention. Administrators can configure retention periods independently for several data categories. Metrics data supports a retention window between 1 month and 13 months. Entities and configuration data can be retained for a minimum of 1 month and a maximum of 3 months. Organization reports support a maximum data retention period of 1,440 days. At the normal retention tier, VCF Operations retains data at 5-minute granularity for 6 months, then rolls up the seventh month into 1-hour aggregations. A real-time retention tier provides 5-minute granularity, a standard tier retains data for 1 month, and a long-term tier retains data for 13 months. Different data retention policies can be configured and controlled for each category according to organizational requirements. Log data is governed separately through VCF Log Management, where administrators define log partitions that each carry their own retention period in days, with logs removed from disk automatically once a partition's period elapses and the option to archive partitions to external NFS or S3 storage for longer-term preservation.
-VCF Operations for Networks provides additional granular retention controls. The default data retention period is 1 month in the advanced license edition. Flow data retention is fixed at a 1-month window within the platform. For organizations that need to retain flow data beyond one month, the Streaming Databus provides a mechanism to export flows to an external subscriber via HTTPS/HTTP for extended retention. Miscellaneous data retention can be configured with up to 100 GB of additional disk space.
-VCF Operations also provides backup capabilities that support regulatory and operational retention needs. Administrators can take regular backups of both custom and out-of-the-box content. When reducing an entity metrics retention period in VCF Operations for Networks, the recommendation is to back up log files first to prevent data loss, which supports the principle of preserving data before modifying retention windows.
-The Consumption layer of VCF, comprising VMware Kubernetes Service (VKS), vSphere Supervisor, and vSphere namespaces, adds Kubernetes-native persistent storage lifecycle controls relevant to data retention for containerized workloads. Persistent volumes in Supervisor namespaces store application data outside the lifecycle of individual pods and workloads, so data remains available when workloads restart or scale. The central mechanism governing retention behavior is the PersistentVolume reclaim policy, which controls what happens to the underlying storage and its data when the associated PersistentVolumeClaim is deleted. The Retain policy preserves the volume and its data in a Released state for manual administrator reclamation, leaving the data intact for inspection, archival, or transfer before final disposal. The Delete policy causes the storage asset to be removed when the claim is released. Retain is the default for manually provisioned PersistentVolumes. StorageClass definitions carry a ReclaimPolicy field that sets the default behavior for all dynamically provisioned volumes within a given storage class, allowing cluster administrators to enforce organization-wide retention defaults at the storage class level rather than per-volume. For StatefulSet workloads, Kubernetes provides a persistentVolumeClaimRetentionPolicy setting with a whenDeleted field that controls whether PVCs and their backing volumes are retained or deleted when the StatefulSet is removed; scaling a StatefulSet down does not delete the associated volumes by default. Organizations subject to retention obligations should configure StorageClasses with the Retain policy so that workload termination does not destroy data that must be kept for a defined period.
-Storage Policy Based Management (SPBM) provides a unified control plane across VKS storage, enabling storage policies to be associated with persistent volumes that capture the storage characteristics required by a given workload or retention regime. VKS clusters surface a storage compliance status per volume: a Compliant status indicates that the datastore backing the volume satisfies the requirements of the associated policy; an Out of Date status indicates the policy has been updated but the new requirements have not yet been communicated to the datastore, requiring the policy to be reapplied to bring the volume back into compliance. This policy-driven model allows administrators to codify storage requirements and verify adherence continuously.
-For Harbor Registry deployments on VKS clusters, administrators should note that configuring a StorageClass or PersistentVolume with a Delete reclaim policy results in all Harbor data being deleted when the Harbor package is removed. Image artifact retention requirements should drive reclaim policy selection for Harbor-backing storage. Platform teams should also manage data protection storage locations in VCF Automation to align with company-specific data residency and infrastructure standards.
-These retention controls apply to the operational, monitoring, and configuration data that VCF Operations collects and manages, and to the persistent volume lifecycle for containerized workloads on VKS. They do not extend to application data stored within virtual machines outside the Kubernetes layer, user-generated content on datastores not managed by Kubernetes, or media outside the VCF platform. Organizations must establish broader data retention policies, classification schemes, and lifecycle management processes that address all media and data types subject to statutory, regulatory, and contractual obligations. VCF's retention settings are one component of a larger retention program that requires organizational governance, legal review of applicable obligations, and potentially additional tools for archival and disposition of data beyond what VCF Operations and VKS storage lifecycle controls manage.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides configurable data retention capabilities for the security telemetry and flow data it collects, contributing to an organization's ability to retain security-relevant data in accordance with statutory, regulatory, and contractual obligations.
-Security Services Platform, which underpins Network Detection and Response (NDR) and related analytics services, offers control over flow data retention. Flow data is retained for 30 days by default via the flow-data-retention setting. If storage capacity is insufficient to handle flow volume from workloads, some flow metadata may be lost, flow ingestion may be paused, or data retention may be reduced dynamically to stay within available storage. Administrators can monitor retention health through the ssp_flow_storage.avg_flow_storage_ratio metric, which reports the ratio of current retention days to predicted full days for flow storage, and through the ssp_analytics_storage.avg_predicted_tabl_retention_days metric, which tracks predicted retention for the correlated flow visualization table (default 30 days). Security Services Platform persistent storage collects data even when the License Hub is offline, providing resilience against brief service interruptions that might otherwise affect data continuity.
-Network Detection and Response retains detection events and campaign data for 12 months, providing a fixed retention window for threat detection artifacts.
-For organizations using cloud-connected vDefend features, Security Services Platform maintains defined retention periods for data collected under active service subscriptions: IDS events and other network events, VM identifiers, rules and policies, conversation history, and security profiles are retained for one year during an active subscription, and for 90 days following subscription expiration.
-Administrators should note that when the Malware Prevention Service feature is deleted, all previously gathered data analytics are permanently removed. Organizations with compliance-driven retention requirements should account for this before decommissioning that service.
-These retention controls allow organizations to align vDefend's security data storage with their compliance requirements. The broader scope of media and data retention across the full infrastructure stack, including operational data, log archives, backup snapshots, and storage-level data protection, is handled by other VCF components such as VCF Operations, VCF Log Management, and vSAN Data Protection.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable retention mechanisms that allow administrators to align disaster recovery and cyber recovery data with retention obligations. PNR snapshot schedules define a retention policy that determines how long each snapshot is retained, with hourly, daily, weekly, and monthly cadences and a maximum retention duration of three years. Administrators can also select predefined retention templates that combine recovery point objective (RPO) and snapshot retention parameters for quick configuration of protection groups.
-For vSphere Replication, the retention policy determines the expiration of point-in-time copies, and storage consumption drops after all point-in-time copies referring to the original disk are expired. Administrators configure the number of retention slots and the spacing between recovery points, so older instances expire automatically once the configured limit is exceeded.
-Cyber Recovery snapshot schedules in PNR follow the same retention model, defining a retention policy that controls how long each snapshot is retained. Administrators should account for storage capacity when configuring longer retention schedules, since extended retention periods increase storage consumption on the underlying datastores.
-These retention controls allow organizations to align disaster recovery and cyber recovery data retention with applicable statutory, regulatory, and contractual obligations. PNR provides the technical mechanisms; determining the specific retention durations that satisfy each obligation is an organizational policy decision.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides configurable backup retention controls that support an organization's data retention requirements for its managed databases. These controls do not define retention obligations, which come from the organization's legal and compliance functions, but they provide the technical means to implement those obligations for PostgreSQL, MySQL, SQL Server, and MinIO data.
-Retention periods are configured through Data Service Policies in the DSM administration interface. Each policy supports a backup-retention-period setting that defines the duration for which backups are kept. When multiple policies apply to a namespace, DSM aggregates the retention constraints by selecting the more restrictive minimum and maximum retention day values, producing a resultant retention window that reflects all applicable policies. Data service policies can also be tailored to specific requirements and enforced across different tenants, giving administrators a consistent mechanism for applying retention standards in multi-tenant deployments.
-For deleted databases, DSM retains automated backups according to the configured retention period and exposes an Archives tab in the administration interface where administrators can access and adjust the retention period of retained backups. This allows organizations to maintain access to backup data even after a database instance has been removed, supporting retention obligations that outlast the operational lifetime of a specific database. When a database is deleted, automated backups continue to be retained until the retention policy is met.
-DSM also supports point-in-time restore within the backup retention period, enabling recovery to any point within the retained window. On-demand backups behave differently from automated backups: they are permanent and do not expire automatically. On-demand backups remain in the backup storage location until an administrator manually deletes them, which means they can consume storage quota indefinitely and require separate tracking for retention compliance.
-Data service policies also define backup storage locations (S3-compatible targets) alongside retention duration. If a data service policy that is in use is deleted, the data services associated with that policy become non-compliant, alerting administrators to a configuration gap.
-Meeting this control fully requires the organization to determine the applicable retention periods, communicate those requirements to DSM administrators, and configure policies accordingly. DSM does not automatically derive retention obligations from regulatory or contractual sources. Its retention controls also cover only the database data it manages and do not address retention of all media and data types that may fall within an organization's broader retention obligations.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
@@ -3232,67 +3215,47 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>VCF provides configurable data retention controls within VCF Operations that allow administrators to align operational data retention periods with organizational requirements. These controls do not address the full scope of media and data retention governance, but they give administrators granular tuning over how long different categories of platform-generated data are kept.
-VCF Operations exposes data retention settings through Administration &gt; Global Settings &gt; Data Retention. Administrators can configure retention periods independently for several data categories. Metrics data supports a retention window between 1 month and 13 months. Entities and configuration data can be retained for a minimum of 1 month and a maximum of 3 months. Organization reports support a maximum data retention period of 1,440 days. At the normal retention tier, VCF Operations retains data at 5-minute granularity for 6 months, then rolls up the seventh month into 1-hour aggregations. A real-time retention tier provides 5-minute granularity, a standard tier retains data for 1 month, and a long-term tier retains data for 13 months. Different data retention policies can be configured and controlled for each category according to organizational requirements. Log data is governed separately through VCF Log Management, where administrators define log partitions that each carry their own retention period in days, with logs removed from disk automatically once a partition's period elapses and the option to archive partitions to external NFS or S3 storage for longer-term preservation.
-VCF Operations for Networks provides additional granular retention controls. The default data retention period is 1 month in the advanced license edition. Flow data retention is fixed at a 1-month window within the platform. For organizations that need to retain flow data beyond one month, the Streaming Databus provides a mechanism to export flows to an external subscriber via HTTPS/HTTP for extended retention. Miscellaneous data retention can be configured with up to 100 GB of additional disk space.
-VCF Operations also provides backup capabilities that support regulatory and operational retention needs. Administrators can take regular backups of both custom and out-of-the-box content. When reducing an entity metrics retention period in VCF Operations for Networks, the recommendation is to back up log files first to prevent data loss, which supports the principle of preserving data before modifying retention windows.
-The Consumption layer of VCF, comprising VMware Kubernetes Service (VKS), vSphere Supervisor, and vSphere namespaces, adds Kubernetes-native persistent storage lifecycle controls relevant to data retention for containerized workloads. Persistent volumes in Supervisor namespaces store application data outside the lifecycle of individual pods and workloads, so data remains available when workloads restart or scale. The central mechanism governing retention behavior is the PersistentVolume reclaim policy, which controls what happens to the underlying storage and its data when the associated PersistentVolumeClaim is deleted. The Retain policy preserves the volume and its data in a Released state for manual administrator reclamation, leaving the data intact for inspection, archival, or transfer before final disposal. The Delete policy causes the storage asset to be removed when the claim is released. Retain is the default for manually provisioned PersistentVolumes. StorageClass definitions carry a ReclaimPolicy field that sets the default behavior for all dynamically provisioned volumes within a given storage class, allowing cluster administrators to enforce organization-wide retention defaults at the storage class level rather than per-volume. For StatefulSet workloads, Kubernetes provides a persistentVolumeClaimRetentionPolicy setting with a whenDeleted field that controls whether PVCs and their backing volumes are retained or deleted when the StatefulSet is removed; scaling a StatefulSet down does not delete the associated volumes by default. Organizations subject to retention obligations should configure StorageClasses with the Retain policy so that workload termination does not destroy data that must be kept for a defined period.
-Storage Policy Based Management (SPBM) provides a unified control plane across VKS storage, enabling storage policies to be associated with persistent volumes that capture the storage characteristics required by a given workload or retention regime. VKS clusters surface a storage compliance status per volume: a Compliant status indicates that the datastore backing the volume satisfies the requirements of the associated policy; an Out of Date status indicates the policy has been updated but the new requirements have not yet been communicated to the datastore, requiring the policy to be reapplied to bring the volume back into compliance. This policy-driven model allows administrators to codify storage requirements and verify adherence continuously.
-For Harbor Registry deployments on VKS clusters, administrators should note that configuring a StorageClass or PersistentVolume with a Delete reclaim policy results in all Harbor data being deleted when the Harbor package is removed. Image artifact retention requirements should drive reclaim policy selection for Harbor-backing storage. Platform teams should also manage data protection storage locations in VCF Automation to align with company-specific data residency and infrastructure standards.
-These retention controls apply to the operational, monitoring, and configuration data that VCF Operations collects and manages, and to the persistent volume lifecycle for containerized workloads on VKS. They do not extend to application data stored within virtual machines outside the Kubernetes layer, user-generated content on datastores not managed by Kubernetes, or media outside the VCF platform. Organizations must establish broader data retention policies, classification schemes, and lifecycle management processes that address all media and data types subject to statutory, regulatory, and contractual obligations. VCF's retention settings are one component of a larger retention program that requires organizational governance, legal review of applicable obligations, and potentially additional tools for archival and disposition of data beyond what VCF Operations and VKS storage lifecycle controls manage.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides configurable data retention capabilities for the security telemetry and flow data it collects, contributing to an organization's ability to retain security-relevant data in accordance with statutory, regulatory, and contractual obligations.
-Security Services Platform, which underpins Network Detection and Response (NDR) and related analytics services, offers control over flow data retention. Flow data is retained for 30 days by default via the flow-data-retention setting. If storage capacity is insufficient to handle flow volume from workloads, some flow metadata may be lost, flow ingestion may be paused, or data retention may be reduced dynamically to stay within available storage. Administrators can monitor retention health through the ssp_flow_storage.avg_flow_storage_ratio metric, which reports the ratio of current retention days to predicted full days for flow storage, and through the ssp_analytics_storage.avg_predicted_tabl_retention_days metric, which tracks predicted retention for the correlated flow visualization table (default 30 days). Security Services Platform persistent storage collects data even when the License Hub is offline, providing resilience against brief service interruptions that might otherwise affect data continuity.
-Network Detection and Response retains detection events and campaign data for 12 months, providing a fixed retention window for threat detection artifacts.
-For organizations using cloud-connected vDefend features, Security Services Platform maintains defined retention periods for data collected under active service subscriptions: IDS events and other network events, VM identifiers, rules and policies, conversation history, and security profiles are retained for one year during an active subscription, and for 90 days following subscription expiration.
-Administrators should note that when the Malware Prevention Service feature is deleted, all previously gathered data analytics are permanently removed. Organizations with compliance-driven retention requirements should account for this before decommissioning that service.
-These retention controls allow organizations to align vDefend's security data storage with their compliance requirements. The broader scope of media and data retention across the full infrastructure stack, including operational data, log archives, backup snapshots, and storage-level data protection, is handled by other VCF components such as VCF Operations, VCF Log Management, and vSAN Data Protection.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable retention mechanisms that allow administrators to align disaster recovery and cyber recovery data with retention obligations. PNR snapshot schedules define a retention policy that determines how long each snapshot is retained, with hourly, daily, weekly, and monthly cadences and a maximum retention duration of three years. Administrators can also select predefined retention templates that combine recovery point objective (RPO) and snapshot retention parameters for quick configuration of protection groups.
-For vSphere Replication, the retention policy determines the expiration of point-in-time copies, and storage consumption drops after all point-in-time copies referring to the original disk are expired. Administrators configure the number of retention slots and the spacing between recovery points, so older instances expire automatically once the configured limit is exceeded.
-Cyber Recovery snapshot schedules in PNR follow the same retention model, defining a retention policy that controls how long each snapshot is retained. Administrators should account for storage capacity when configuring longer retention schedules, since extended retention periods increase storage consumption on the underlying datastores.
-These retention controls allow organizations to align disaster recovery and cyber recovery data retention with applicable statutory, regulatory, and contractual obligations. PNR provides the technical mechanisms; determining the specific retention durations that satisfy each obligation is an organizational policy decision.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides configurable backup retention controls that support an organization's data retention requirements for its managed databases. These controls do not define retention obligations, which come from the organization's legal and compliance functions, but they provide the technical means to implement those obligations for PostgreSQL, MySQL, SQL Server, and MinIO data.
-Retention periods are configured through Data Service Policies in the DSM administration interface. Each policy supports a backup-retention-period setting that defines the duration for which backups are kept. When multiple policies apply to a namespace, DSM aggregates the retention constraints by selecting the more restrictive minimum and maximum retention day values, producing a resultant retention window that reflects all applicable policies. Data service policies can also be tailored to specific requirements and enforced across different tenants, giving administrators a consistent mechanism for applying retention standards in multi-tenant deployments.
-For deleted databases, DSM retains automated backups according to the configured retention period and exposes an Archives tab in the administration interface where administrators can access and adjust the retention period of retained backups. This allows organizations to maintain access to backup data even after a database instance has been removed, supporting retention obligations that outlast the operational lifetime of a specific database. When a database is deleted, automated backups continue to be retained until the retention policy is met.
-DSM also supports point-in-time restore within the backup retention period, enabling recovery to any point within the retained window. On-demand backups behave differently from automated backups: they are permanent and do not expire automatically. On-demand backups remain in the backup storage location until an administrator manually deletes them, which means they can consume storage quota indefinitely and require separate tracking for retention compliance.
-Data service policies also define backup storage locations (S3-compatible targets) alongside retention duration. If a data service policy that is in use is deleted, the data services associated with that policy become non-compliant, alerting administrators to a configuration gap.
-Meeting this control fully requires the organization to determine the applicable retention periods, communicate those requirements to DSM administrators, and configure policies accordingly. DSM does not automatically derive retention obligations from regulatory or contractual sources. Its retention controls also cover only the database data it manages and do not address retention of all media and data types that may fall within an organization's broader retention obligations.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
@@ -3324,53 +3287,37 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>The control requires granting assessors minimum necessary access to conduct conformity assessments, including logical access to design, development, production, inspection, and testing artifacts, as well as physical access to facilities. VCF provides granular role-based access control mechanisms across its components that allow organizations to create appropriately scoped accounts for assessors conducting compliance or security assessments.
-VMware vCenter implements a privilege system where privileges are grouped into roles that can be mapped to users or groups. The platform includes a built-in Read Only role that grants three system-defined privileges (System.Anonymous, System.View, and System.Read), providing a baseline for assessor access that allows viewing configuration and operational data without the ability to modify the environment. Read privileges can be assigned at the datacenter or vCenter level, allowing organizations to scope assessor visibility to specific portions of the infrastructure. For more tailored access, vCenter supports custom role creation with granular privilege assignment and permission propagation to vSphere objects, enabling organizations to build assessor-specific roles that include only the privileges needed for a particular assessment engagement. The operator role in vCenter provides another restricted authorization level where users can view information about vCenter but cannot alter its configuration. VCF SSO also includes a SystemConfiguration.ReadOnly privilege that grants members read-only access to vCenter appliance operations under Appliance Management, providing a targeted option for assessors whose scope includes appliance configuration review. New users and groups are assigned the No Access role by default in vCenter, so assessor accounts start with no visibility and require explicit permission assignments before any infrastructure objects become accessible.
-VCF Operations provides its own ReadOnly role that allows users to perform read operations but restricts write actions such as create, update, or delete. Permissions for specific functional areas, such as Infrastructure Operations and the Analyze page, are managed in the Roles tab under Administration &gt; Control Panel, where individual permissions can be selected or deselected when adding or editing a role. This granularity allows organizations to tailor assessor access to the specific operational data relevant to the assessment scope.
-VCF Automation includes several roles suited to assessor access. The Organization Auditor role provides read-only access equivalent to the Organization Administrator role, allowing auditors to view anything an administrator can see without the ability to edit or manage users and groups. The Project Auditor role is similarly restricted to read-only access at the project level. The Project Viewer role is restricted to read-only access, except in cases where viewers can perform non-destructive actions such as downloading cloud templates. Organizations can also create custom user roles in VCF Automation to expand or restrict permissions for specific project resources without granting broader administrative capability.
-The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS), vSphere Supervisor, and vSphere namespaces, provides a dedicated access control framework for granting assessors minimum-necessary access to Kubernetes workloads and related artifacts. At the vSphere Namespace level, administrators can assign VCF SSO users and groups to one of three permission levels: Can View, Can Edit, or Owner. The Can View role grants read-only access to VKS cluster objects provisioned in the namespace and maps no permissions to Kubernetes roles within those clusters, making it appropriate for assessors who need to review namespace-scoped workload configurations without the ability to modify cluster resources. VCF Consumption CLI access to vSphere Namespaces is enforced based on user permissions, and users without sufficient permissions cannot connect to the Supervisor or its VKS clusters. Within VKS clusters, Kubernetes RBAC provides the built-in view ClusterRole, which gives read-only access to most objects in a namespace but excludes visibility into roles and role bindings, allowing assessors to inspect workload and policy configurations without being able to examine or modify the cluster's access control structure. Administrators can also create custom Roles and RoleBindings scoped to specific namespaces, and Kubernetes ABAC rules support a readonly access mode to restrict users to read-only operations on specified resources. Kubernetes RBAC enforces that a RoleBinding cannot grant permissions the grantor does not already hold, which prevents privilege escalation when provisioning assessor accounts. RoleBinding subjects in VKS clusters must reference VCF SSO user or group names, keeping assessor identity management integrated with the platform's central identity directory. Access to the VKS Policy Insights page, which provides centralized visibility into the governance health of the VKS cluster estate, is restricted to the Organization Auditor and related roles, allowing organizations to grant assessors read-only policy visibility without broader operational rights. Harbor Registry, available as a standard package on VKS clusters, enforces RBAC to control access to container image artifacts, allowing organizations to grant assessors read access to specific image repositories relevant to their assessment scope.
-The platform's authorization model verifies what objects each principal has access to, and the recommendation across VCF components is to configure users with the specific privileges required for their role rather than assigning overly permissive roles. Organizations should define assessor-specific roles in each VCF component that grant read access only to the artifacts relevant to the assessment scope.
-VCF supports identity federation through standard protocols, which allows assessor accounts to be provisioned through an organization's existing identity provider rather than creating local accounts. Identity provider federation uses token-based authentication and supports multifactor authentication. This simplifies lifecycle management and helps ensure assessor credentials are deprovisioned when the engagement ends.
-VCF also provides audit logging capabilities that create a record of assessor actions during an engagement. VCF Operations user activity audit reports provide traceability of user activities including logging in, actions on clusters and nodes, changes to system passwords, activating certificates, and logging out. These audit logs can be downloaded in PDF or XLS format. VCF Automation audit logs capture action details including timestamps, user names, project names, and trace IDs. This auditability allows organizations to verify that assessors operated within the bounds of their granted access.
-Physical access to facilities is outside VCF's scope as a software platform. Organizations must address physical facility access through their own site security and visitor management processes.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to granting assessors minimum necessary logical access through the role-based access control (RBAC) framework of its Security Services Platform. The framework defines three permission levels: Full Access, which encompasses create, read, update, and delete operations; Read, which provides read-only visibility; and No Access, which excludes all operations.
-A dedicated Auditor role is available for personnel who need to review configurations without making changes. In VMware vDefend, the Auditor role holds Read permissions for platform operations including deploying, managing, and upgrading the Security Services Platform, configuring authentication and authorization, performing server configuration, managing backup and restore, and activating Security Intelligence. The Auditor role also has Full Access to view Rule Analysis results and download rule analysis reports, giving assessors the ability to examine how firewall policy rules align with observed traffic behavior. For other operations, including exporting data, publishing segmentation policies and group definitions, managing discovery and inventory assets, and configuring Security Intelligence data collection, the Auditor role holds Restricted permissions that limit its ability to alter state.
-Five platform roles are defined with differentiated permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Enterprise Admin and Security Engineer hold Full Access to export traffic flows, monitor infrastructure, environment, and application telemetry, configure Security Intelligence data collection, and visualize traffic flows. This role hierarchy allows administrators to assign the Auditor role to assessors while granting elevated operational permissions only to engineering and administrative staff.
-Physical access to facilities is outside the scope of VMware vDefend and must be addressed through separate facility access management processes and organizational controls.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides role-based access control (RBAC) mechanisms that support granting assessors minimum necessary logical access to disaster recovery artifacts.
-PNR restricts login to VMware vCenter administrators by default; other users require an explicit permission grant from an administrator to access PNR. Permissions are required on both vCenter objects and PNR-specific objects, giving administrators granular control over what each user can see and do within the platform. PNR also verifies permissions on the remote vCenter instance as part of its access control validation, making the permission model consistent across sites in a two-site configuration.
-For assessors who need access to recovery plan operations without full administrative rights, permissions for testing and running recovery plans can be assigned separately in PNR. In shared recovery site configurations, the vCenter administrator manages PNR permissions so that each user has sufficient privileges to configure and use protection and recovery for their own protected site without access to resources belonging to other organizations. Site-wide permission assignments must be added on a per-site basis, with corresponding permissions required on both the protected and recovery sites. Users or user groups assigned a PNR role that are not vCenter administrators do not obtain vSphere Replication privileges; assessors who require access to both PNR operations and vSphere Replication should be placed in separate user groups for each role type, avoiding the need to grant full vCenter administrator privileges.
-When PNR is deployed with VCF Automation, access is controlled through role-based permissions assigned to Provider Administrators, Organization Administrators, Project Administrators, and Project Advanced Users, providing additional scoping options for multi-tenant environments.
-PNR also includes a Clean Room Orchestrator where access is restricted to IP addresses and IP address ranges configured in a management access list, limiting which hosts can reach the clean room environment used for ransomware recovery and analysis.
-Physical access to facilities is outside the scope of PNR and remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
@@ -3385,16 +3332,12 @@
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides role-based access control in the Avi Controller that administrators can use to create role-scoped accounts for assessors, granting minimum necessary access to the application delivery environment. Avi roles define two distinct access types: Write privilege allows users to create, read, modify, and delete resources, while Read privilege restricts users to reading existing configuration, viewing health and analytics data, and viewing audit logs without modification capability. This allows assessor accounts to be provisioned with observation-only access across the application delivery tier.
-Avi includes a dedicated Auditor role that grants Read access to view security services platform configuration, upgrades, and authentication and authorization configuration in the Avi Controller without the ability to make changes. Assessors can be assigned this role to gain visibility into the security posture of the application delivery environment without receiving any write capability.
-Within the Controller administration interface, accounts can be assigned to specific roles and tenants, allowing narrowly scoped access to virtual service configurations, WAF policies, application analytics, SSL/TLS certificate profiles, health monitor definitions, analytics profiles, and application event and audit logs. Avi's extended granular role-based access control also supports sub-resource-level permissions, enabling role definitions that restrict access to specific pool sub-resources. The ability to export certificates and private keys is separately controlled through RBAC, and Avi documentation recommends restricting this capability to the fewest number of administrators possible.
-Avi supports local accounts and integration with external identity providers including LDAP, SAML, TACACS+, and OAuth/OIDC, allowing organizations to provision assessor accounts through existing identity governance processes rather than creating standalone credentials. Role assignments can be scoped to specific tenants, which is useful when an assessment covers only a subset of the application delivery environment. In Kubernetes deployments using the Avi Kubernetes Operator (AKO), the ako-all-tenants-permission-controller role provides cross-tenant read access for assessors who need visibility across multiple namespaces.
-This control asks whether the organization grants assessors minimum necessary access to design, development, production, inspection, and testing artifacts, and whether physical access to facilities is managed. Avi's RBAC addresses the application delivery tier. Meeting this control in full requires the organization to define the scope of each assessment, coordinate access provisioning across all relevant VCF platform components, and manage physical access to facilities. None of those dimensions fall within Avi's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -3848,53 +3791,37 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>The control requires granting assessors minimum necessary access to conduct conformity assessments, including logical access to design, development, production, inspection, and testing artifacts, as well as physical access to facilities. VCF provides granular role-based access control mechanisms across its components that allow organizations to create appropriately scoped accounts for assessors conducting compliance or security assessments.
-VMware vCenter implements a privilege system where privileges are grouped into roles that can be mapped to users or groups. The platform includes a built-in Read Only role that grants three system-defined privileges (System.Anonymous, System.View, and System.Read), providing a baseline for assessor access that allows viewing configuration and operational data without the ability to modify the environment. Read privileges can be assigned at the datacenter or vCenter level, allowing organizations to scope assessor visibility to specific portions of the infrastructure. For more tailored access, vCenter supports custom role creation with granular privilege assignment and permission propagation to vSphere objects, enabling organizations to build assessor-specific roles that include only the privileges needed for a particular assessment engagement. The operator role in vCenter provides another restricted authorization level where users can view information about vCenter but cannot alter its configuration. VCF SSO also includes a SystemConfiguration.ReadOnly privilege that grants members read-only access to vCenter appliance operations under Appliance Management, providing a targeted option for assessors whose scope includes appliance configuration review. New users and groups are assigned the No Access role by default in vCenter, so assessor accounts start with no visibility and require explicit permission assignments before any infrastructure objects become accessible.
-VCF Operations provides its own ReadOnly role that allows users to perform read operations but restricts write actions such as create, update, or delete. Permissions for specific functional areas, such as Infrastructure Operations and the Analyze page, are managed in the Roles tab under Administration &gt; Control Panel, where individual permissions can be selected or deselected when adding or editing a role. This granularity allows organizations to tailor assessor access to the specific operational data relevant to the assessment scope.
-VCF Automation includes several roles suited to assessor access. The Organization Auditor role provides read-only access equivalent to the Organization Administrator role, allowing auditors to view anything an administrator can see without the ability to edit or manage users and groups. The Project Auditor role is similarly restricted to read-only access at the project level. The Project Viewer role is restricted to read-only access, except in cases where viewers can perform non-destructive actions such as downloading cloud templates. Organizations can also create custom user roles in VCF Automation to expand or restrict permissions for specific project resources without granting broader administrative capability.
-The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS), vSphere Supervisor, and vSphere namespaces, provides a dedicated access control framework for granting assessors minimum-necessary access to Kubernetes workloads and related artifacts. At the vSphere Namespace level, administrators can assign VCF SSO users and groups to one of three permission levels: Can View, Can Edit, or Owner. The Can View role grants read-only access to VKS cluster objects provisioned in the namespace and maps no permissions to Kubernetes roles within those clusters, making it appropriate for assessors who need to review namespace-scoped workload configurations without the ability to modify cluster resources. VCF Consumption CLI access to vSphere Namespaces is enforced based on user permissions, and users without sufficient permissions cannot connect to the Supervisor or its VKS clusters. Within VKS clusters, Kubernetes RBAC provides the built-in view ClusterRole, which gives read-only access to most objects in a namespace but excludes visibility into roles and role bindings, allowing assessors to inspect workload and policy configurations without being able to examine or modify the cluster's access control structure. Administrators can also create custom Roles and RoleBindings scoped to specific namespaces, and Kubernetes ABAC rules support a readonly access mode to restrict users to read-only operations on specified resources. Kubernetes RBAC enforces that a RoleBinding cannot grant permissions the grantor does not already hold, which prevents privilege escalation when provisioning assessor accounts. RoleBinding subjects in VKS clusters must reference VCF SSO user or group names, keeping assessor identity management integrated with the platform's central identity directory. Access to the VKS Policy Insights page, which provides centralized visibility into the governance health of the VKS cluster estate, is restricted to the Organization Auditor and related roles, allowing organizations to grant assessors read-only policy visibility without broader operational rights. Harbor Registry, available as a standard package on VKS clusters, enforces RBAC to control access to container image artifacts, allowing organizations to grant assessors read access to specific image repositories relevant to their assessment scope.
-The platform's authorization model verifies what objects each principal has access to, and the recommendation across VCF components is to configure users with the specific privileges required for their role rather than assigning overly permissive roles. Organizations should define assessor-specific roles in each VCF component that grant read access only to the artifacts relevant to the assessment scope.
-VCF supports identity federation through standard protocols, which allows assessor accounts to be provisioned through an organization's existing identity provider rather than creating local accounts. Identity provider federation uses token-based authentication and supports multifactor authentication. This simplifies lifecycle management and helps ensure assessor credentials are deprovisioned when the engagement ends.
-VCF also provides audit logging capabilities that create a record of assessor actions during an engagement. VCF Operations user activity audit reports provide traceability of user activities including logging in, actions on clusters and nodes, changes to system passwords, activating certificates, and logging out. These audit logs can be downloaded in PDF or XLS format. VCF Automation audit logs capture action details including timestamps, user names, project names, and trace IDs. This auditability allows organizations to verify that assessors operated within the bounds of their granted access.
-Physical access to facilities is outside VCF's scope as a software platform. Organizations must address physical facility access through their own site security and visitor management processes.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to granting assessors minimum necessary logical access through the role-based access control (RBAC) framework of its Security Services Platform. The framework defines three permission levels: Full Access, which encompasses create, read, update, and delete operations; Read, which provides read-only visibility; and No Access, which excludes all operations.
-A dedicated Auditor role is available for personnel who need to review configurations without making changes. In VMware vDefend, the Auditor role holds Read permissions for platform operations including deploying, managing, and upgrading the Security Services Platform, configuring authentication and authorization, performing server configuration, managing backup and restore, and activating Security Intelligence. The Auditor role also has Full Access to view Rule Analysis results and download rule analysis reports, giving assessors the ability to examine how firewall policy rules align with observed traffic behavior. For other operations, including exporting data, publishing segmentation policies and group definitions, managing discovery and inventory assets, and configuring Security Intelligence data collection, the Auditor role holds Restricted permissions that limit its ability to alter state.
-Five platform roles are defined with differentiated permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Enterprise Admin and Security Engineer hold Full Access to export traffic flows, monitor infrastructure, environment, and application telemetry, configure Security Intelligence data collection, and visualize traffic flows. This role hierarchy allows administrators to assign the Auditor role to assessors while granting elevated operational permissions only to engineering and administrative staff.
-Physical access to facilities is outside the scope of VMware vDefend and must be addressed through separate facility access management processes and organizational controls.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides role-based access control (RBAC) mechanisms that support granting assessors minimum necessary logical access to disaster recovery artifacts.
-PNR restricts login to VMware vCenter administrators by default; other users require an explicit permission grant from an administrator to access PNR. Permissions are required on both vCenter objects and PNR-specific objects, giving administrators granular control over what each user can see and do within the platform. PNR also verifies permissions on the remote vCenter instance as part of its access control validation, making the permission model consistent across sites in a two-site configuration.
-For assessors who need access to recovery plan operations without full administrative rights, permissions for testing and running recovery plans can be assigned separately in PNR. In shared recovery site configurations, the vCenter administrator manages PNR permissions so that each user has sufficient privileges to configure and use protection and recovery for their own protected site without access to resources belonging to other organizations. Site-wide permission assignments must be added on a per-site basis, with corresponding permissions required on both the protected and recovery sites. Users or user groups assigned a PNR role that are not vCenter administrators do not obtain vSphere Replication privileges; assessors who require access to both PNR operations and vSphere Replication should be placed in separate user groups for each role type, avoiding the need to grant full vCenter administrator privileges.
-When PNR is deployed with VCF Automation, access is controlled through role-based permissions assigned to Provider Administrators, Organization Administrators, Project Administrators, and Project Advanced Users, providing additional scoping options for multi-tenant environments.
-PNR also includes a Clean Room Orchestrator where access is restricted to IP addresses and IP address ranges configured in a management access list, limiting which hosts can reach the clean room environment used for ransomware recovery and analysis.
-Physical access to facilities is outside the scope of PNR and remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
@@ -3909,16 +3836,12 @@
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides role-based access control in the Avi Controller that administrators can use to create role-scoped accounts for assessors, granting minimum necessary access to the application delivery environment. Avi roles define two distinct access types: Write privilege allows users to create, read, modify, and delete resources, while Read privilege restricts users to reading existing configuration, viewing health and analytics data, and viewing audit logs without modification capability. This allows assessor accounts to be provisioned with observation-only access across the application delivery tier.
-Avi includes a dedicated Auditor role that grants Read access to view security services platform configuration, upgrades, and authentication and authorization configuration in the Avi Controller without the ability to make changes. Assessors can be assigned this role to gain visibility into the security posture of the application delivery environment without receiving any write capability.
-Within the Controller administration interface, accounts can be assigned to specific roles and tenants, allowing narrowly scoped access to virtual service configurations, WAF policies, application analytics, SSL/TLS certificate profiles, health monitor definitions, analytics profiles, and application event and audit logs. Avi's extended granular role-based access control also supports sub-resource-level permissions, enabling role definitions that restrict access to specific pool sub-resources. The ability to export certificates and private keys is separately controlled through RBAC, and Avi documentation recommends restricting this capability to the fewest number of administrators possible.
-Avi supports local accounts and integration with external identity providers including LDAP, SAML, TACACS+, and OAuth/OIDC, allowing organizations to provision assessor accounts through existing identity governance processes rather than creating standalone credentials. Role assignments can be scoped to specific tenants, which is useful when an assessment covers only a subset of the application delivery environment. In Kubernetes deployments using the Avi Kubernetes Operator (AKO), the ako-all-tenants-permission-controller role provides cross-tenant read access for assessors who need visibility across multiple namespaces.
-This control asks whether the organization grants assessors minimum necessary access to design, development, production, inspection, and testing artifacts, and whether physical access to facilities is managed. Avi's RBAC addresses the application delivery tier. Meeting this control in full requires the organization to define the scope of each assessment, coordinate access provisioning across all relevant VCF platform components, and manage physical access to facilities. None of those dimensions fall within Avi's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -4228,39 +4151,27 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in compliance measurement, scoring, and reporting capabilities that support an organization's conformity assessment activities. These tools allow operators to evaluate the state of their VCF environment against established security benchmarks and internal policies, producing quantitative results that can feed into broader compliance assessment programs. While conducting a full compliance program assessment is an organizational responsibility, VCF provides the technical instrumentation needed to assess and report on infrastructure conformity.
-VCF Operations includes a compliance scoring engine that measures how well objects in the environment conform to industrial, governmental, regulatory, or internal standards, including the DISA STIG. The compliance score is calculated as the ratio of compliant objects to the total number of objects assessed by a given benchmark, expressed as a percentage. When an object violates multiple standards, the compliance score reflects the most critical violation, so the worst-case posture is visible. The compliance score card displays 100 when all objects are compliant, and shows the count of non-compliant symptoms when violations exist. The Badge|Compliance metric provides a per-object compliance percentage based on triggered symptoms versus total symptoms. Compliance scores are calculated for all objects in the environment regardless of the viewing user's object-level permissions, so the assessment reflects the true state of the environment rather than a filtered view.
-VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Compliance alerts appear as violations to the standard, and the triggered symptoms appear as violated rules. The Compliance Alert List displays alerts that caused compliance violations in a sortable table, allowing administrators to prioritize remediation efforts. These alerts, combined with remediation guidance, help administrators move from assessment findings to corrective action.
-NSX provides a compliance report capability that allows administrators to compare their NSX networking configuration against IT policies and industry standards. This report identifies areas where the configuration deviates from the selected benchmark, supporting targeted remediation as part of an assessment cycle.
-At the VMware vCenter level, the Compliance interface compares the desired configuration state against the current state of each host in a cluster and calculates drift. The ClusterCompliance or HostCompliance object returned by the compliance check API contains the per-host compliance status, notifications, and check duration, and administrators can retrieve cluster compliance status through the REST API by calling the Compliance.get endpoint. This mechanism checks conformity with the cluster's configured desired state rather than with a regulatory benchmark directly, but when the desired state profile is built to match a regulatory baseline, the drift check supports ongoing assessment against that baseline.
-VCF's security configuration guidance, including the Security Configuration Guide and the DISA STIG, provides prescriptive baselines that organizations can use as the reference standard for their conformity assessments. VCF supports compliance measurement against guidelines for protecting controlled unclassified information. Administrators can automate assessment and remediation workflows through product interfaces, command-line tools, and APIs, reducing the manual effort involved in preparing for and responding to compliance assessments. VCF Operations also supports running workflows to remediate alerts or automate tasks, and maps out-of-the-box workflows to recommendations for automated remediation.
-These capabilities allow organizations to run repeatable, evidence-based conformity assessments against their VCF infrastructure, but the broader assessment program, including determining which laws, regulations, and contractual obligations apply, selecting assessment frameworks, scheduling assessment cycles, engaging independent auditors where required, and acting on assessment findings, remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to conformity assessments through Security Services Platform's Security Segmentation scoring and assessment capabilities, which provide measurable, evidence-based evaluation of an organization's network microsegmentation posture.
-Security Services Platform calculates a Security Segmentation Score on a 100-point weighted scale distributed across five categories. Points are awarded only when firewall rules and configuration meet specified requirements, giving compliance officers a quantitative metric to track microsegmentation maturity over time. The scoring system supports Relaxed mode, useful for gauging progress during segmentation implementation, and Strict mode, which applies stricter penalties for unidentified or unsegmented traffic for more stringent posture assessment. These modes allow organizations to choose the assessment rigor appropriate to their compliance posture.
-Environment Protection assessment evaluates whether workloads are protected by environment-specific segmentation policies, such as Dev, Prod, and Test. It measures the percentage of environment pairs operating in blocked mode and the percentage of all workloads covered by at least one environment rule, providing concrete metrics that can be presented during conformity assessments. The Security Segmentation Report includes an Inter-Environment Pair Protection Rule Action Summary section that provides a tabular summary of inter-environment communications, suitable for inclusion in audit evidence packages.
-The Security Segmentation Score Breakdown report provides more granular detail, listing total environments and pairs, protection rule action summaries, and identifying environment pairs that lack inter-environment policies. This breakdown allows auditors to pinpoint specific gaps in microsegmentation coverage rather than relying solely on the aggregate score.
-Rule Analysis, available within Security Services Platform, supports scheduled or on-demand analysis of the complete VMware vDefend (DFW) configuration. It detects contradictions where two rules have the same configuration with different actions, and identifies shadowed rules by comparing effective group memberships. Rule Analysis results can be exported as a CSV report for archival and review by external assessors. Role-based access control for Rule Analysis is enforced through Security Services Platform's platform roles; Enterprise Admin has full access to run, view, and download Rule Analysis reports. These capabilities help organizations demonstrate that their firewall policy is internally consistent and that analysis artifacts are available for auditor review.
-Security Intelligence, integrated within Security Services Platform in VMware vDefend, provides policy recommendations that can be reviewed, modified, and published to enforce network security policies. The View Impacted Flows capability displays unprotected traffic flows used to generate policy recommendations, giving auditors direct visibility into unprotected network paths.
-These vDefend capabilities address the network security dimension of conformity assessments. The broader compliance assessment program, including determining which regulations apply, selecting assessment frameworks, engaging assessors, and evaluating non-network controls, remains an organizational responsibility outside the scope of vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -4312,39 +4223,27 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in compliance measurement, scoring, and reporting capabilities that support an organization's conformity assessment activities. These tools allow operators to evaluate the state of their VCF environment against established security benchmarks and internal policies, producing quantitative results that can feed into broader compliance assessment programs. While conducting a full compliance program assessment is an organizational responsibility, VCF provides the technical instrumentation needed to assess and report on infrastructure conformity.
-VCF Operations includes a compliance scoring engine that measures how well objects in the environment conform to industrial, governmental, regulatory, or internal standards, including the DISA STIG. The compliance score is calculated as the ratio of compliant objects to the total number of objects assessed by a given benchmark, expressed as a percentage. When an object violates multiple standards, the compliance score reflects the most critical violation, so the worst-case posture is visible. The compliance score card displays 100 when all objects are compliant, and shows the count of non-compliant symptoms when violations exist. The Badge|Compliance metric provides a per-object compliance percentage based on triggered symptoms versus total symptoms. Compliance scores are calculated for all objects in the environment regardless of the viewing user's object-level permissions, so the assessment reflects the true state of the environment rather than a filtered view.
-VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Compliance alerts appear as violations to the standard, and the triggered symptoms appear as violated rules. The Compliance Alert List displays alerts that caused compliance violations in a sortable table, allowing administrators to prioritize remediation efforts. These alerts, combined with remediation guidance, help administrators move from assessment findings to corrective action.
-NSX provides a compliance report capability that allows administrators to compare their NSX networking configuration against IT policies and industry standards. This report identifies areas where the configuration deviates from the selected benchmark, supporting targeted remediation as part of an assessment cycle.
-At the VMware vCenter level, the Compliance interface compares the desired configuration state against the current state of each host in a cluster and calculates drift. The ClusterCompliance or HostCompliance object returned by the compliance check API contains the per-host compliance status, notifications, and check duration, and administrators can retrieve cluster compliance status through the REST API by calling the Compliance.get endpoint. This mechanism checks conformity with the cluster's configured desired state rather than with a regulatory benchmark directly, but when the desired state profile is built to match a regulatory baseline, the drift check supports ongoing assessment against that baseline.
-VCF's security configuration guidance, including the Security Configuration Guide and the DISA STIG, provides prescriptive baselines that organizations can use as the reference standard for their conformity assessments. VCF supports compliance measurement against guidelines for protecting controlled unclassified information. Administrators can automate assessment and remediation workflows through product interfaces, command-line tools, and APIs, reducing the manual effort involved in preparing for and responding to compliance assessments. VCF Operations also supports running workflows to remediate alerts or automate tasks, and maps out-of-the-box workflows to recommendations for automated remediation.
-These capabilities allow organizations to run repeatable, evidence-based conformity assessments against their VCF infrastructure, but the broader assessment program, including determining which laws, regulations, and contractual obligations apply, selecting assessment frameworks, scheduling assessment cycles, engaging independent auditors where required, and acting on assessment findings, remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to conformity assessments through Security Services Platform's Security Segmentation scoring and assessment capabilities, which provide measurable, evidence-based evaluation of an organization's network microsegmentation posture.
-Security Services Platform calculates a Security Segmentation Score on a 100-point weighted scale distributed across five categories. Points are awarded only when firewall rules and configuration meet specified requirements, giving compliance officers a quantitative metric to track microsegmentation maturity over time. The scoring system supports Relaxed mode, useful for gauging progress during segmentation implementation, and Strict mode, which applies stricter penalties for unidentified or unsegmented traffic for more stringent posture assessment. These modes allow organizations to choose the assessment rigor appropriate to their compliance posture.
-Environment Protection assessment evaluates whether workloads are protected by environment-specific segmentation policies, such as Dev, Prod, and Test. It measures the percentage of environment pairs operating in blocked mode and the percentage of all workloads covered by at least one environment rule, providing concrete metrics that can be presented during conformity assessments. The Security Segmentation Report includes an Inter-Environment Pair Protection Rule Action Summary section that provides a tabular summary of inter-environment communications, suitable for inclusion in audit evidence packages.
-The Security Segmentation Score Breakdown report provides more granular detail, listing total environments and pairs, protection rule action summaries, and identifying environment pairs that lack inter-environment policies. This breakdown allows auditors to pinpoint specific gaps in microsegmentation coverage rather than relying solely on the aggregate score.
-Rule Analysis, available within Security Services Platform, supports scheduled or on-demand analysis of the complete VMware vDefend (DFW) configuration. It detects contradictions where two rules have the same configuration with different actions, and identifies shadowed rules by comparing effective group memberships. Rule Analysis results can be exported as a CSV report for archival and review by external assessors. Role-based access control for Rule Analysis is enforced through Security Services Platform's platform roles; Enterprise Admin has full access to run, view, and download Rule Analysis reports. These capabilities help organizations demonstrate that their firewall policy is internally consistent and that analysis artifacts are available for auditor review.
-Security Intelligence, integrated within Security Services Platform in VMware vDefend, provides policy recommendations that can be reviewed, modified, and published to enforce network security policies. The View Impacted Flows capability displays unprotected traffic flows used to generate policy recommendations, giving auditors direct visibility into unprotected network paths.
-These vDefend capabilities address the network security dimension of conformity assessments. The broader compliance assessment program, including determining which regulations apply, selecting assessment frameworks, engaging assessors, and evaluating non-network controls, remains an organizational responsibility outside the scope of vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -4396,39 +4295,27 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in compliance measurement, scoring, and reporting capabilities that support an organization's conformity assessment activities. These tools allow operators to evaluate the state of their VCF environment against established security benchmarks and internal policies, producing quantitative results that can feed into broader compliance assessment programs. While conducting a full compliance program assessment is an organizational responsibility, VCF provides the technical instrumentation needed to assess and report on infrastructure conformity.
-VCF Operations includes a compliance scoring engine that measures how well objects in the environment conform to industrial, governmental, regulatory, or internal standards, including the DISA STIG. The compliance score is calculated as the ratio of compliant objects to the total number of objects assessed by a given benchmark, expressed as a percentage. When an object violates multiple standards, the compliance score reflects the most critical violation, so the worst-case posture is visible. The compliance score card displays 100 when all objects are compliant, and shows the count of non-compliant symptoms when violations exist. The Badge|Compliance metric provides a per-object compliance percentage based on triggered symptoms versus total symptoms. Compliance scores are calculated for all objects in the environment regardless of the viewing user's object-level permissions, so the assessment reflects the true state of the environment rather than a filtered view.
-VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Compliance alerts appear as violations to the standard, and the triggered symptoms appear as violated rules. The Compliance Alert List displays alerts that caused compliance violations in a sortable table, allowing administrators to prioritize remediation efforts. These alerts, combined with remediation guidance, help administrators move from assessment findings to corrective action.
-NSX provides a compliance report capability that allows administrators to compare their NSX networking configuration against IT policies and industry standards. This report identifies areas where the configuration deviates from the selected benchmark, supporting targeted remediation as part of an assessment cycle.
-At the VMware vCenter level, the Compliance interface compares the desired configuration state against the current state of each host in a cluster and calculates drift. The ClusterCompliance or HostCompliance object returned by the compliance check API contains the per-host compliance status, notifications, and check duration, and administrators can retrieve cluster compliance status through the REST API by calling the Compliance.get endpoint. This mechanism checks conformity with the cluster's configured desired state rather than with a regulatory benchmark directly, but when the desired state profile is built to match a regulatory baseline, the drift check supports ongoing assessment against that baseline.
-VCF's security configuration guidance, including the Security Configuration Guide and the DISA STIG, provides prescriptive baselines that organizations can use as the reference standard for their conformity assessments. VCF supports compliance measurement against guidelines for protecting controlled unclassified information. Administrators can automate assessment and remediation workflows through product interfaces, command-line tools, and APIs, reducing the manual effort involved in preparing for and responding to compliance assessments. VCF Operations also supports running workflows to remediate alerts or automate tasks, and maps out-of-the-box workflows to recommendations for automated remediation.
-These capabilities allow organizations to run repeatable, evidence-based conformity assessments against their VCF infrastructure, but the broader assessment program, including determining which laws, regulations, and contractual obligations apply, selecting assessment frameworks, scheduling assessment cycles, engaging independent auditors where required, and acting on assessment findings, remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to conformity assessments through Security Services Platform's Security Segmentation scoring and assessment capabilities, which provide measurable, evidence-based evaluation of an organization's network microsegmentation posture.
-Security Services Platform calculates a Security Segmentation Score on a 100-point weighted scale distributed across five categories. Points are awarded only when firewall rules and configuration meet specified requirements, giving compliance officers a quantitative metric to track microsegmentation maturity over time. The scoring system supports Relaxed mode, useful for gauging progress during segmentation implementation, and Strict mode, which applies stricter penalties for unidentified or unsegmented traffic for more stringent posture assessment. These modes allow organizations to choose the assessment rigor appropriate to their compliance posture.
-Environment Protection assessment evaluates whether workloads are protected by environment-specific segmentation policies, such as Dev, Prod, and Test. It measures the percentage of environment pairs operating in blocked mode and the percentage of all workloads covered by at least one environment rule, providing concrete metrics that can be presented during conformity assessments. The Security Segmentation Report includes an Inter-Environment Pair Protection Rule Action Summary section that provides a tabular summary of inter-environment communications, suitable for inclusion in audit evidence packages.
-The Security Segmentation Score Breakdown report provides more granular detail, listing total environments and pairs, protection rule action summaries, and identifying environment pairs that lack inter-environment policies. This breakdown allows auditors to pinpoint specific gaps in microsegmentation coverage rather than relying solely on the aggregate score.
-Rule Analysis, available within Security Services Platform, supports scheduled or on-demand analysis of the complete VMware vDefend (DFW) configuration. It detects contradictions where two rules have the same configuration with different actions, and identifies shadowed rules by comparing effective group memberships. Rule Analysis results can be exported as a CSV report for archival and review by external assessors. Role-based access control for Rule Analysis is enforced through Security Services Platform's platform roles; Enterprise Admin has full access to run, view, and download Rule Analysis reports. These capabilities help organizations demonstrate that their firewall policy is internally consistent and that analysis artifacts are available for auditor review.
-Security Intelligence, integrated within Security Services Platform in VMware vDefend, provides policy recommendations that can be reviewed, modified, and published to enforce network security policies. The View Impacted Flows capability displays unprotected traffic flows used to generate policy recommendations, giving auditors direct visibility into unprotected network paths.
-These vDefend capabilities address the network security dimension of conformity assessments. The broader compliance assessment program, including determining which regulations apply, selecting assessment frameworks, engaging assessors, and evaluating non-network controls, remains an organizational responsibility outside the scope of vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -4480,39 +4367,27 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in compliance measurement, scoring, and reporting capabilities that support an organization's conformity assessment activities. These tools allow operators to evaluate the state of their VCF environment against established security benchmarks and internal policies, producing quantitative results that can feed into broader compliance assessment programs. While conducting a full compliance program assessment is an organizational responsibility, VCF provides the technical instrumentation needed to assess and report on infrastructure conformity.
-VCF Operations includes a compliance scoring engine that measures how well objects in the environment conform to industrial, governmental, regulatory, or internal standards, including the DISA STIG. The compliance score is calculated as the ratio of compliant objects to the total number of objects assessed by a given benchmark, expressed as a percentage. When an object violates multiple standards, the compliance score reflects the most critical violation, so the worst-case posture is visible. The compliance score card displays 100 when all objects are compliant, and shows the count of non-compliant symptoms when violations exist. The Badge|Compliance metric provides a per-object compliance percentage based on triggered symptoms versus total symptoms. Compliance scores are calculated for all objects in the environment regardless of the viewing user's object-level permissions, so the assessment reflects the true state of the environment rather than a filtered view.
-VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Compliance alerts appear as violations to the standard, and the triggered symptoms appear as violated rules. The Compliance Alert List displays alerts that caused compliance violations in a sortable table, allowing administrators to prioritize remediation efforts. These alerts, combined with remediation guidance, help administrators move from assessment findings to corrective action.
-NSX provides a compliance report capability that allows administrators to compare their NSX networking configuration against IT policies and industry standards. This report identifies areas where the configuration deviates from the selected benchmark, supporting targeted remediation as part of an assessment cycle.
-At the VMware vCenter level, the Compliance interface compares the desired configuration state against the current state of each host in a cluster and calculates drift. The ClusterCompliance or HostCompliance object returned by the compliance check API contains the per-host compliance status, notifications, and check duration, and administrators can retrieve cluster compliance status through the REST API by calling the Compliance.get endpoint. This mechanism checks conformity with the cluster's configured desired state rather than with a regulatory benchmark directly, but when the desired state profile is built to match a regulatory baseline, the drift check supports ongoing assessment against that baseline.
-VCF's security configuration guidance, including the Security Configuration Guide and the DISA STIG, provides prescriptive baselines that organizations can use as the reference standard for their conformity assessments. VCF supports compliance measurement against guidelines for protecting controlled unclassified information. Administrators can automate assessment and remediation workflows through product interfaces, command-line tools, and APIs, reducing the manual effort involved in preparing for and responding to compliance assessments. VCF Operations also supports running workflows to remediate alerts or automate tasks, and maps out-of-the-box workflows to recommendations for automated remediation.
-These capabilities allow organizations to run repeatable, evidence-based conformity assessments against their VCF infrastructure, but the broader assessment program, including determining which laws, regulations, and contractual obligations apply, selecting assessment frameworks, scheduling assessment cycles, engaging independent auditors where required, and acting on assessment findings, remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to conformity assessments through Security Services Platform's Security Segmentation scoring and assessment capabilities, which provide measurable, evidence-based evaluation of an organization's network microsegmentation posture.
-Security Services Platform calculates a Security Segmentation Score on a 100-point weighted scale distributed across five categories. Points are awarded only when firewall rules and configuration meet specified requirements, giving compliance officers a quantitative metric to track microsegmentation maturity over time. The scoring system supports Relaxed mode, useful for gauging progress during segmentation implementation, and Strict mode, which applies stricter penalties for unidentified or unsegmented traffic for more stringent posture assessment. These modes allow organizations to choose the assessment rigor appropriate to their compliance posture.
-Environment Protection assessment evaluates whether workloads are protected by environment-specific segmentation policies, such as Dev, Prod, and Test. It measures the percentage of environment pairs operating in blocked mode and the percentage of all workloads covered by at least one environment rule, providing concrete metrics that can be presented during conformity assessments. The Security Segmentation Report includes an Inter-Environment Pair Protection Rule Action Summary section that provides a tabular summary of inter-environment communications, suitable for inclusion in audit evidence packages.
-The Security Segmentation Score Breakdown report provides more granular detail, listing total environments and pairs, protection rule action summaries, and identifying environment pairs that lack inter-environment policies. This breakdown allows auditors to pinpoint specific gaps in microsegmentation coverage rather than relying solely on the aggregate score.
-Rule Analysis, available within Security Services Platform, supports scheduled or on-demand analysis of the complete VMware vDefend (DFW) configuration. It detects contradictions where two rules have the same configuration with different actions, and identifies shadowed rules by comparing effective group memberships. Rule Analysis results can be exported as a CSV report for archival and review by external assessors. Role-based access control for Rule Analysis is enforced through Security Services Platform's platform roles; Enterprise Admin has full access to run, view, and download Rule Analysis reports. These capabilities help organizations demonstrate that their firewall policy is internally consistent and that analysis artifacts are available for auditor review.
-Security Intelligence, integrated within Security Services Platform in VMware vDefend, provides policy recommendations that can be reviewed, modified, and published to enforce network security policies. The View Impacted Flows capability displays unprotected traffic flows used to generate policy recommendations, giving auditors direct visibility into unprotected network paths.
-These vDefend capabilities address the network security dimension of conformity assessments. The broader compliance assessment program, including determining which regulations apply, selecting assessment frameworks, engaging assessors, and evaluating non-network controls, remains an organizational responsibility outside the scope of vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -5128,95 +5003,57 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>VCF enforces least privilege through a granular role-based access control (RBAC) model that spans all major platform components. Permissions are scoped both by function and by inventory location, so users can perform only the activities specified by the role assigned to them on the specific object to which that role is assigned.
-VMware vCenter implements a privilege model where privileges are system-defined requirements associated with vSphere managed objects. These privileges are defined by VMware and cannot be changed by client applications, which means the privilege boundaries are enforced at the platform level. Privileges are fine-grained access controls that can be grouped into roles, providing precise control over what actions each user can perform. Users are granted access through roles, which are predefined sets of privileges mapped to users or groups on specific objects.
-vCenter ships with several built-in roles that enforce varying levels of access restriction. The three permanent system roles, Administrator, Read Only, and No Access, cannot be deleted or edited; new users and groups are assigned the No Access role by default, so access must be explicitly granted before a user can view or change any object. The Read Only role grants only three system-defined privileges: System.Anonymous, System.View, and System.Read. The Operator role is the most restricted authorization level available, allowing users to view information about vCenter but not alter its configuration. For cryptographic operations, a dedicated No Cryptography Administrator role provides all Administrator privileges except Cryptographic Operations, so that only users explicitly assigned the Cryptographic Operations privileges can perform encryption-related tasks. If a predefined role does not meet specific needs, administrators can create custom roles containing only the minimum set of required privileges. For users who require administrative access to virtual machine configuration but should not be able to run commands inside a guest operating system, the platform supports creating a custom role that excludes the Virtual machine &gt; Guest operations privilege.
-vCenter also provides a privilege check recording feature that monitors which privileges are checked during vCenter operations. The PrivilegeChecks service interface provides operations for retrieving a list of the latest privilege checks along with the corresponding sessions, users, managed objects, and operation IDs. Administrators can use this capability to identify which privileges are actually exercised during a workflow and build roles with only the minimum privileges needed for specific operations.
-VCF Operations implements its own RBAC system where users can only perform the actions that their permissions allow. The ReadOnly role provides read-only access, allowing users to perform read operations but restricting write actions such as create, update, or delete. The VCF Operations documentation recommends that the administrators role be assigned only to specific users who must access objects and perform actions across the entire environment. Local VCF Operations users and vCenter users should be configured with the specific privileges required for their role to avoid unexpected access from overly permissive role assignments. Even integration adapters follow least privilege principles: the Management Pack for Oracle Database, for example, requires creation of a least-privileged user with minimum database user privileges. The Management Pack for Kubernetes similarly requires that user-defined custom roles provide read-only access to all cluster resources and the Kubernetes API.
-VCF Automation supports organization-specific roles that can be assigned only to users within the organization to which they belong. Organization users can use only those rights from their roles that are published to their organizations. Organization administrators can create custom roles to grant selected users permissions to perform specific tasks or access content outside of their default organization roles, enabling precise scoping of access. System administrators manage access to projects and catalog items through entitlement policies using user criteria, providing another layer of access control that restricts what resources users can request and consume. The cloud_admin service role satisfies the minimum service role requirement for VCF Automation API access, and the Cloudadmin role provides host switch-level permissions within VCF Automation.
-At the Consumption layer, VMware Kubernetes Service (VKS) and vSphere Supervisor implement two complementary tiers of least privilege: namespace-level permissions and Kubernetes RBAC within clusters. vSphere Namespace permissions for VCF SSO users and groups are assigned through three roles: Can View (read-only access to VKS cluster objects provisioned in the namespace, with no permissions mapped to Kubernetes roles within those clusters), Can Edit (modification rights), and Owner (full administrative control). The VCF Consumption CLI enforces these role assignments at the API boundary; VCF SSO users who lack sufficient permissions on a vSphere Namespace receive an "Error from server (Forbidden)" response and cannot connect to Supervisor or VKS clusters. Administrative operations on Supervisor Services require a discrete "Manage Supervisor Services" privilege on VMware vCenter, scoped separately from general vSphere Administrator access. Content library administration similarly requires specific permissions beyond the vSphere Administrator role, with individual permissions assignable through custom roles when the full Administrator role is not appropriate.
-Within VKS clusters, Kubernetes RBAC provides fine-grained access control through Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings. RBAC rules are expressed in terms of specific resource types and verbs (get, list, create, delete, and so on), with guidance that specific resources and verbs be used rather than wildcard entries, so only the permissions required for a workload to function correctly are applied. Platform Operators and DevOps users are assigned non-admin or custom roles scoped to their responsibilities; Developer users receive read-only or no roles by default. Kubernetes RBAC supports least privilege for ServiceAccounts as well: by creating ServiceAccounts with narrow RBAC bindings and attaching them to workloads, pods operate with only the permissions they require rather than inheriting broad cluster-level access. Separating ServiceAccount creation from human user onboarding makes it practical to maintain least privilege for automated workloads independently of human access management. RBAC should be used to enforce least-privilege access to Secret objects specifically, given the sensitive nature of credential material. Administrators can use kubectl auth can-i with user impersonation to verify what actions other users can perform, supporting least privilege verification without requiring direct credential access. IAM role trust policies in the Consumption layer should be scoped to specific service accounts and namespaces to enforce least privilege boundaries at the identity-to-workload level. Kubernetes RBAC enforces binding constraints: a user creating or updating a RoleBinding or ClusterRoleBinding can only grant permissions they themselves hold, and a user creating or updating a Role or ClusterRole cannot add permissions beyond their own. Where limited delegation is needed, the bind verb can be scoped to specific named roles, so administrators cannot delegate access beyond what they are themselves authorized to grant. Periodic review of RBAC settings for redundant entries and potential escalation paths supports ongoing least-privilege hygiene.
-VKS clusters apply least privilege at the workload level through Pod Security Admission (PSA). PSA supports three profiles: Privileged (unrestricted, permits known privilege escalations), Baseline (minimally restrictive, blocks known privilege escalation vectors while allowing the default minimal pod configuration), and Restricted (a hardened profile that follows least privilege, requiring non-root execution and restricting Linux capabilities). The Restricted profile is the recommended target for workloads that should operate with least privilege. Kubernetes also allows granting specific Linux capabilities to a container process without granting all privileges of the root user, enabling capability-level access scoping for workloads that require specific kernel permissions without full privilege. The Supervisor secret injection agent runs with allowPrivilegeEscalation set to false, blocking privilege escalation at the platform component level. Cluster administrators should understand privilege escalation paths introduced by create and update permissions on workloads that can reference arbitrary ServiceAccounts, and should restrict those permissions accordingly.
-Centralized authentication through VCF SSO means that privilege assignments are consistently enforced across vCenter, VMware ESX, NSX, and VCF Operations. VCF Operations integrates with VCF SSO for centralized user and group authentication and management, and supports single sign-on to enable secure user login.
-The platform documentation explicitly recommends that user accounts be given the minimal number of privileges required to perform their assigned tasks. When predefined roles are too permissive for a given use case, custom roles should be created containing only the minimum set of required privileges. For Kubernetes environments, administrators are directed to use a least-privileged kubeconfig for routine operations and to reserve break-glass access only for emergency situations.
-VMware Private AI Services (PAIS) supports the concept of least privilege through a layered set of access controls that scope permissions to specific roles, groups, and project membership across the AI platform.
-PAIS access is controlled through OIDC group-based authorization. The authorizedGroups configuration specifies which OIDC groups may access PAIS endpoints, and only user accounts that are members of those groups can reach the service. The same model applies whether activation is performed through the VCF Automation UI (via the oidc-authorized-groups setting) or through kubectl. PAIS activation requires coordination with the OIDC provider administrator to define identity and access management before users can be granted access.
-Access to AI catalog items in VCF Automation is gated by explicit permission grants. DevOps engineers and other consumers must receive permission from an organization administrator before they can request GPU-accelerated VMware Kubernetes Service (VKS) clusters or deep learning VM catalog items. When importing PAIS namespaces from VMware VCF Automation 8.18 into VCF Automation, users with the Project Viewer role must be reassigned the Project Auditor role, scoping read-only access to the new tenancy model.
-For ML model storage in Harbor, PAIS scopes access at the project level. Harbor project read-write permissions are required to store models, restricting access to sensitive training and tuning data by Harbor project role. Only users with assigned project roles can push or pull model artifacts.
-Role assignment for AI workload deployment is explicit and requires an authorized administrator. The organization administrator must assign the required user role before users can deploy deep learning VMs, and VI administrators must have appropriate permissions on the underlying vSphere cluster to deploy DL VM templates. VCF Automation uses separate scoped tokens for provider-level and tenant-level operations: a PROVIDER_ADMIN_ACCESS_TOKEN for provider scope and a TENANT_ADMIN_ACCESS_TOKEN for organization administrator scope, keeping administrative privileges partitioned by function.
-The Grafana observability layer for PAIS supports role-based access through OIDC group mapping. The grafana-oidc-role-mapping configuration assigns the Admin role to users matching a designated OIDC group attribute and the Viewer role to other authenticated users, scoping write access to the observability platform to a named administrator group.
-Deep Learning VM deployment uses restricted cloud-init file permissions to control access to initialization and workload execution code, with executable permissions (0755) for application scripts and restricted permissions (0600) for network configuration files. When configuring external data sources for Knowledge Bases, PAIS specifies that the integration service account should be created with no assigned roles as its starting state, and Google Drive folders used as data sources must be shared with the service account using view-only permissions.
-Tenant isolation extends to compute allocation: organization region quotas in PAIS can be assigned from single or multiple supervisors, with CPU and memory limits and reservations configured per zone, scoping resource consumption to the limits set by the provider administrator.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend implements the principle of least privilege at two levels: network access control for workloads and role-based access control for its own administrative interfaces.
-At the network layer, the vDefend distributed firewall (DFW) restricts workload-to-workload communication to only those flows explicitly permitted by policy. Default-deny rule bases mean no network path is open unless a rule specifically allows it. Microsegmentation policies can be scoped to individual workloads, security groups, or application tiers, so each workload receives only the network access required to function. Governance guidance in the 9.1 documentation advises administrators to avoid overly permissive rules such as "ANY/ANY/ANY ALLOW" and to define rules that permit only the specific protocols, ports, and source-destination pairs each application needs.
-A new capability in 9.1, Privileged Labels, strengthens workload-level least privilege by anchoring firewall rules to immutable, organization-defined labels that namespace users cannot remove from virtual machines. This mechanism keeps workloads within their assigned security groups so they remain subject to the applicable firewall policies regardless of attempts by lower-privileged namespace users to move them out of scope.
-For administrative access to vDefend itself, Security Services Platform (SSP) enforces role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Role permissions are differentiated by operation: the Enterprise Admin role holds Full Access (FA) to deploy, manage, upgrade, configure authentication and authorization, perform server configuration, and activate Security Intelligence for SSP. The Security Operator role holds Restricted (R) permissions covering Security Intelligence data collection configuration, infrastructure and environment monitoring, and segmentation policy publication, without access to service activation or administrative configuration. Enterprise Administrator privileges are specifically required for high-privilege operations including activating the Malware Prevention Service, deleting Malware Prevention Service features, and accessing User Management to modify role assignments. Administrative privileges are also required to administer compute entity classifications in Security Intelligence. The same five-role structure governs Security Intelligence and Rule Analysis operations within SSP, with each role receiving only the permissions appropriate to its function.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) supports least privilege through role-based access control with a defined set of predefined roles and the ability to clone and customize roles for narrower operational scope. The 9.1 release consolidates Site Recovery Manager and vSphere Replication management under a single permissions model where PNR augments vCenter roles and permissions with additional permissions that allow detailed control over PNR-specific tasks and operations. PNR also verifies permissions on the remote vCenter instance as part of its access control validation, so privilege assignments are evaluated at both sites.
-By default, PNR restricts login access to vCenter administrators; other users must be explicitly granted access by an administrator through the PNR interface. Users or user groups assigned a PNR role who are not vCenter administrators do not obtain vSphere Replication privileges, because PNR roles do not include the privileges of vSphere Replication roles. A user who is not a vCenter administrator but requires privileges to perform both PNR and vSphere Replication operations should be added to two user groups, one for each role type, to avoid granting vCenter administrator privileges.
-vSphere Replication uses role-based access control with predefined roles that can be cloned and customized by adding or removing privileges based on organizational needs. PNR supports role propagation to child objects in the inventory hierarchy, allowing administrators to extend privileges from parent objects such as folders to all virtual machines within them, or to assign permissions at specific inventory levels without propagation when narrower scope is required. When permissions are assigned without propagation, users must have at least Read-only permission on all parent objects in the vCenter inventory.
-PNR for VCF Automation access is controlled through role-based permissions assigned to Provider Administrators, Organization Administrators, Project Administrators, and Project Advanced Users, aligning RBAC with VCF Automation tenancy boundaries. Namespace unpair operations require Organization Administrator role authorization. In shared recovery site configurations, PNR restricts users from changing roles or assigning permissions for objects not dedicated to their own use, which helps prevent unauthorized privilege escalation across tenants, and the vCenter administrator manages PNR permissions so that each user has sufficient privileges to configure and use PNR but no user has access to resources belonging to other tenants.
-PNR requires separate privilege assignment for testing a recovery plan and running a recovery plan, which helps prevent unintended changes at both sites that would require significant time and effort to reverse. PNR roles that allow users to run commands on PNR Server should be assigned to trusted administrator-level users only, and PNR server access should be limited to administrators to reduce the number of accounts available to an attacker. PNR administrators can assign SrmAdministrator or SrmProtectionGroupsAdministrator roles to the automatic protection user or user groups for managing automatic protection permissions.
-For the 9.1 Clean Room Orchestrator, at least one user must be assigned the Organization Owner role to enable administrative access to all resources in the Organization, with additional roles available for narrower delegation. VCF Operations orchestrator workflows for PNR require administrator credentials to access and execute, which restricts non-administrative users from performing sensitive recovery operations through the orchestration interface.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L60" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) implements least privilege across its two primary user roles: Admin and User. The separation is enforced at the platform level and reflected throughout the console interface.
-Users assigned to the DSM User role can view and manage only the database objects they own. They cannot access or modify objects belonging to other users or manage platform-wide configuration. The DSM console restricts the views and actions available based on the assigned role, so User-role accounts see only the subset of the interface relevant to their scope. Administrators have access to the full environment and can create, monitor, and manage all data services, but this elevated scope is reserved for accounts explicitly assigned to the Admin role.
-User and role management is performed through the vSphere Client Permissions interface under the Data Services Manager Configure tab. Administrators can create local users through the DSM UI and assign namespace access through the Permissions view. DSM also supports LDAPS-sourced identities, allowing organizations to map directory service groups to DSM roles and manage access centrally. DSM clears the VMware vCenter administrator credentials secret after successful registration, limiting credential exposure during the initial configuration process.
-DSM applies least privilege at the database level across all supported database engines. PostgreSQL database instances support the GRANT command to assign specific privileges on databases and schemas to individual database users. LDAPS-authenticated PostgreSQL users can be granted specific privileges, including database-level and schema-level access, through explicit GRANT assignments. MySQL LDAPS-authenticated users can be granted specific privileges using the GRANT command to restrict access to designated databases. The default MySQL database user is not a MySQL superuser; it is granted a defined set of privileges for data and schema operations, limiting access to what is required for typical database management. Only the database owner can perform administrator password changes on a given instance, restricting credential management to the party responsible for that database.
-For SQL Server instances, DSM creates a cluster administrator login that does not receive full sysadmin privileges. Instead, DSM grants this login restricted server-level privileges for server management and auditing operations, such as the ability to alter connections and view server state. DSM maintains a separate dsm_mgmt internal management login that restricts user access to system-level objects, keeping administrative operations within an isolated context. SQL Server instance provisioning and server-level configuration management, including Active Directory integration and high availability settings, is restricted to DSM administrators only.
-VCF Automation namespaces that are externally managed in DSM are treated as read-only, restricting modifications to objects whose lifecycle is governed outside DSM. Infrastructure policy configuration requires that the responsible administrator hold the appropriate DSM permissions. These constraints limit what each actor in the system can modify based on their role and the ownership of the resources involved.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N60" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides native role-based access control (RBAC) at the Avi Controller level, covering administrative access to all Avi-managed resources including virtual services, pools, application profiles, certificates, and GSLB configuration. The RBAC framework supports four access types per resource: Write (full create, read, modify, and delete access), Read (view-only access to configuration, health, and analytics data without modification capability), No Access (complete exclusion, including inability to read or list the resource), and Assorted (a mixture of different privilege levels for different resources within a system area). These types are assigned per resource, so a given role can combine read-only access to some areas with full write access to others. The Avi Controller enforces these constraints at runtime; users can access resources only to the extent their assigned role permits.
-When predefined privilege levels do not match the access needs of a particular user account, the Avi Controller supports custom role creation. Administrators create roles that specify a targeted combination of write, read, no-access, or assorted permissions for each resource area. This is configured in the Avi Controller UI under User Authentication and Authorization &gt; User Roles. The Avi documentation recommends creating custom users and roles with limited privileges when the use case does not require System-admin or admin access, rather than assigning broad administrative rights.
-The Extended Granular RBAC feature adds label-based scoping to access control. The allow_unlabelled_access parameter on a role object controls whether users assigned that role can see resources that have not been tagged with labels, enabling access to be scoped to specific application groups or object subsets rather than the entire Controller inventory. Certain permissions classified under Operations and Administration are not supported for role-based access control per application using labels; those must be managed at the global role level. For Auth Mapping Profile configurations, the role and tenant configured for the Any Group or Any Attribute rule should be set to least privilege, as the least-privileged access takes effect after login when no specific group match exists.
-Certificate and key management access is subject to RBAC restrictions. The Avi Controller documentation specifies that the ability to export certificates and keys must be restricted to the fewest number of administrators possible using role-based access control. Write access to Virtual Service, Application Profile, SSL/TLS Certificates, and Certificate Management Profile objects can be scoped to specific roles without granting broader administrative rights.
-GSLB administration is covered separately within Avi's RBAC. Roles can be created that grant write access only to GSLB service resources without providing broader Controller-level access. For GSLB scenarios that do not require System-admin or admin user privileges, Avi's documentation recommends creating a custom user and role with limited permissions rather than assigning the full System-Admin role. Avi GSLB supports creation of non-admin users with assigned roles for granular access control.
-In VCF deployments using organization-managed mode, Avi Load Balancer applies a tiered administrative model. The Provider or Load Balancer Administrator manages resource assignments to organizations and enforces quotas and resource boundaries. An organization administrator must be logged in to edit a Service Engine Group. Project Administrators can deploy and manage load balancing for their applications without waiting for organization administrator intervention, while being restricted from altering Service Engine Group properties such as capacity and placement. This model maps load balancing management authority to the appropriate organizational scope.
-At the integration boundary with VMware vCenter, the Avi Cloud Connector uses a vCenter user account that must have only the minimal set of permissions Avi requires. Two roles must be created for the vCenter Cloud Connector integration: one with global privileges (Avi-Global-Role) and another with folder-level privileges (Avi-Folder-Role). The Avi-Global-Role must be assigned with the Propagate to children option selected to apply permissions to all child objects. The vCenter account user must be assigned the Avi-Folder-Role to the folders containing Service Engine VMs in the vCenter inventory. vCenter cloud access modes include no-access (Avi Controller has no access to vCenter resources), read-access (integration with read-only access), and write-access (full automation of Service Engine creation and placement), allowing deployments to operate with the minimum vCenter access level needed for the deployment scenario.
-Least privilege for the compute, storage, and network fabric underlying the Avi Controller and Service Engine virtual machines is a VCF platform responsibility. Organizations must design Avi role assignments that correspond to job functions and apply them to user accounts for this control to take full effect across the environment.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -10431,39 +10268,27 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in compliance measurement, scoring, and reporting capabilities that support an organization's conformity assessment activities. These tools allow operators to evaluate the state of their VCF environment against established security benchmarks and internal policies, producing quantitative results that can feed into broader compliance assessment programs. While conducting a full compliance program assessment is an organizational responsibility, VCF provides the technical instrumentation needed to assess and report on infrastructure conformity.
-VCF Operations includes a compliance scoring engine that measures how well objects in the environment conform to industrial, governmental, regulatory, or internal standards, including the DISA STIG. The compliance score is calculated as the ratio of compliant objects to the total number of objects assessed by a given benchmark, expressed as a percentage. When an object violates multiple standards, the compliance score reflects the most critical violation, so the worst-case posture is visible. The compliance score card displays 100 when all objects are compliant, and shows the count of non-compliant symptoms when violations exist. The Badge|Compliance metric provides a per-object compliance percentage based on triggered symptoms versus total symptoms. Compliance scores are calculated for all objects in the environment regardless of the viewing user's object-level permissions, so the assessment reflects the true state of the environment rather than a filtered view.
-VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Compliance alerts appear as violations to the standard, and the triggered symptoms appear as violated rules. The Compliance Alert List displays alerts that caused compliance violations in a sortable table, allowing administrators to prioritize remediation efforts. These alerts, combined with remediation guidance, help administrators move from assessment findings to corrective action.
-NSX provides a compliance report capability that allows administrators to compare their NSX networking configuration against IT policies and industry standards. This report identifies areas where the configuration deviates from the selected benchmark, supporting targeted remediation as part of an assessment cycle.
-At the VMware vCenter level, the Compliance interface compares the desired configuration state against the current state of each host in a cluster and calculates drift. The ClusterCompliance or HostCompliance object returned by the compliance check API contains the per-host compliance status, notifications, and check duration, and administrators can retrieve cluster compliance status through the REST API by calling the Compliance.get endpoint. This mechanism checks conformity with the cluster's configured desired state rather than with a regulatory benchmark directly, but when the desired state profile is built to match a regulatory baseline, the drift check supports ongoing assessment against that baseline.
-VCF's security configuration guidance, including the Security Configuration Guide and the DISA STIG, provides prescriptive baselines that organizations can use as the reference standard for their conformity assessments. VCF supports compliance measurement against guidelines for protecting controlled unclassified information. Administrators can automate assessment and remediation workflows through product interfaces, command-line tools, and APIs, reducing the manual effort involved in preparing for and responding to compliance assessments. VCF Operations also supports running workflows to remediate alerts or automate tasks, and maps out-of-the-box workflows to recommendations for automated remediation.
-These capabilities allow organizations to run repeatable, evidence-based conformity assessments against their VCF infrastructure, but the broader assessment program, including determining which laws, regulations, and contractual obligations apply, selecting assessment frameworks, scheduling assessment cycles, engaging independent auditors where required, and acting on assessment findings, remains an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to conformity assessments through Security Services Platform's Security Segmentation scoring and assessment capabilities, which provide measurable, evidence-based evaluation of an organization's network microsegmentation posture.
-Security Services Platform calculates a Security Segmentation Score on a 100-point weighted scale distributed across five categories. Points are awarded only when firewall rules and configuration meet specified requirements, giving compliance officers a quantitative metric to track microsegmentation maturity over time. The scoring system supports Relaxed mode, useful for gauging progress during segmentation implementation, and Strict mode, which applies stricter penalties for unidentified or unsegmented traffic for more stringent posture assessment. These modes allow organizations to choose the assessment rigor appropriate to their compliance posture.
-Environment Protection assessment evaluates whether workloads are protected by environment-specific segmentation policies, such as Dev, Prod, and Test. It measures the percentage of environment pairs operating in blocked mode and the percentage of all workloads covered by at least one environment rule, providing concrete metrics that can be presented during conformity assessments. The Security Segmentation Report includes an Inter-Environment Pair Protection Rule Action Summary section that provides a tabular summary of inter-environment communications, suitable for inclusion in audit evidence packages.
-The Security Segmentation Score Breakdown report provides more granular detail, listing total environments and pairs, protection rule action summaries, and identifying environment pairs that lack inter-environment policies. This breakdown allows auditors to pinpoint specific gaps in microsegmentation coverage rather than relying solely on the aggregate score.
-Rule Analysis, available within Security Services Platform, supports scheduled or on-demand analysis of the complete VMware vDefend (DFW) configuration. It detects contradictions where two rules have the same configuration with different actions, and identifies shadowed rules by comparing effective group memberships. Rule Analysis results can be exported as a CSV report for archival and review by external assessors. Role-based access control for Rule Analysis is enforced through Security Services Platform's platform roles; Enterprise Admin has full access to run, view, and download Rule Analysis reports. These capabilities help organizations demonstrate that their firewall policy is internally consistent and that analysis artifacts are available for auditor review.
-Security Intelligence, integrated within Security Services Platform in VMware vDefend, provides policy recommendations that can be reviewed, modified, and published to enforce network security policies. The View Impacted Flows capability displays unprotected traffic flows used to generate policy recommendations, giving auditors direct visibility into unprotected network paths.
-These vDefend capabilities address the network security dimension of conformity assessments. The broader compliance assessment program, including determining which regulations apply, selecting assessment frameworks, engaging assessors, and evaluating non-network controls, remains an organizational responsibility outside the scope of vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr">
@@ -10803,67 +10628,47 @@
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>VCF provides configurable data retention controls within VCF Operations that allow administrators to align operational data retention periods with organizational requirements. These controls do not address the full scope of media and data retention governance, but they give administrators granular tuning over how long different categories of platform-generated data are kept.
-VCF Operations exposes data retention settings through Administration &gt; Global Settings &gt; Data Retention. Administrators can configure retention periods independently for several data categories. Metrics data supports a retention window between 1 month and 13 months. Entities and configuration data can be retained for a minimum of 1 month and a maximum of 3 months. Organization reports support a maximum data retention period of 1,440 days. At the normal retention tier, VCF Operations retains data at 5-minute granularity for 6 months, then rolls up the seventh month into 1-hour aggregations. A real-time retention tier provides 5-minute granularity, a standard tier retains data for 1 month, and a long-term tier retains data for 13 months. Different data retention policies can be configured and controlled for each category according to organizational requirements. Log data is governed separately through VCF Log Management, where administrators define log partitions that each carry their own retention period in days, with logs removed from disk automatically once a partition's period elapses and the option to archive partitions to external NFS or S3 storage for longer-term preservation.
-VCF Operations for Networks provides additional granular retention controls. The default data retention period is 1 month in the advanced license edition. Flow data retention is fixed at a 1-month window within the platform. For organizations that need to retain flow data beyond one month, the Streaming Databus provides a mechanism to export flows to an external subscriber via HTTPS/HTTP for extended retention. Miscellaneous data retention can be configured with up to 100 GB of additional disk space.
-VCF Operations also provides backup capabilities that support regulatory and operational retention needs. Administrators can take regular backups of both custom and out-of-the-box content. When reducing an entity metrics retention period in VCF Operations for Networks, the recommendation is to back up log files first to prevent data loss, which supports the principle of preserving data before modifying retention windows.
-The Consumption layer of VCF, comprising VMware Kubernetes Service (VKS), vSphere Supervisor, and vSphere namespaces, adds Kubernetes-native persistent storage lifecycle controls relevant to data retention for containerized workloads. Persistent volumes in Supervisor namespaces store application data outside the lifecycle of individual pods and workloads, so data remains available when workloads restart or scale. The central mechanism governing retention behavior is the PersistentVolume reclaim policy, which controls what happens to the underlying storage and its data when the associated PersistentVolumeClaim is deleted. The Retain policy preserves the volume and its data in a Released state for manual administrator reclamation, leaving the data intact for inspection, archival, or transfer before final disposal. The Delete policy causes the storage asset to be removed when the claim is released. Retain is the default for manually provisioned PersistentVolumes. StorageClass definitions carry a ReclaimPolicy field that sets the default behavior for all dynamically provisioned volumes within a given storage class, allowing cluster administrators to enforce organization-wide retention defaults at the storage class level rather than per-volume. For StatefulSet workloads, Kubernetes provides a persistentVolumeClaimRetentionPolicy setting with a whenDeleted field that controls whether PVCs and their backing volumes are retained or deleted when the StatefulSet is removed; scaling a StatefulSet down does not delete the associated volumes by default. Organizations subject to retention obligations should configure StorageClasses with the Retain policy so that workload termination does not destroy data that must be kept for a defined period.
-Storage Policy Based Management (SPBM) provides a unified control plane across VKS storage, enabling storage policies to be associated with persistent volumes that capture the storage characteristics required by a given workload or retention regime. VKS clusters surface a storage compliance status per volume: a Compliant status indicates that the datastore backing the volume satisfies the requirements of the associated policy; an Out of Date status indicates the policy has been updated but the new requirements have not yet been communicated to the datastore, requiring the policy to be reapplied to bring the volume back into compliance. This policy-driven model allows administrators to codify storage requirements and verify adherence continuously.
-For Harbor Registry deployments on VKS clusters, administrators should note that configuring a StorageClass or PersistentVolume with a Delete reclaim policy results in all Harbor data being deleted when the Harbor package is removed. Image artifact retention requirements should drive reclaim policy selection for Harbor-backing storage. Platform teams should also manage data protection storage locations in VCF Automation to align with company-specific data residency and infrastructure standards.
-These retention controls apply to the operational, monitoring, and configuration data that VCF Operations collects and manages, and to the persistent volume lifecycle for containerized workloads on VKS. They do not extend to application data stored within virtual machines outside the Kubernetes layer, user-generated content on datastores not managed by Kubernetes, or media outside the VCF platform. Organizations must establish broader data retention policies, classification schemes, and lifecycle management processes that address all media and data types subject to statutory, regulatory, and contractual obligations. VCF's retention settings are one component of a larger retention program that requires organizational governance, legal review of applicable obligations, and potentially additional tools for archival and disposition of data beyond what VCF Operations and VKS storage lifecycle controls manage.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides configurable data retention capabilities for the security telemetry and flow data it collects, contributing to an organization's ability to retain security-relevant data in accordance with statutory, regulatory, and contractual obligations.
-Security Services Platform, which underpins Network Detection and Response (NDR) and related analytics services, offers control over flow data retention. Flow data is retained for 30 days by default via the flow-data-retention setting. If storage capacity is insufficient to handle flow volume from workloads, some flow metadata may be lost, flow ingestion may be paused, or data retention may be reduced dynamically to stay within available storage. Administrators can monitor retention health through the ssp_flow_storage.avg_flow_storage_ratio metric, which reports the ratio of current retention days to predicted full days for flow storage, and through the ssp_analytics_storage.avg_predicted_tabl_retention_days metric, which tracks predicted retention for the correlated flow visualization table (default 30 days). Security Services Platform persistent storage collects data even when the License Hub is offline, providing resilience against brief service interruptions that might otherwise affect data continuity.
-Network Detection and Response retains detection events and campaign data for 12 months, providing a fixed retention window for threat detection artifacts.
-For organizations using cloud-connected vDefend features, Security Services Platform maintains defined retention periods for data collected under active service subscriptions: IDS events and other network events, VM identifiers, rules and policies, conversation history, and security profiles are retained for one year during an active subscription, and for 90 days following subscription expiration.
-Administrators should note that when the Malware Prevention Service feature is deleted, all previously gathered data analytics are permanently removed. Organizations with compliance-driven retention requirements should account for this before decommissioning that service.
-These retention controls allow organizations to align vDefend's security data storage with their compliance requirements. The broader scope of media and data retention across the full infrastructure stack, including operational data, log archives, backup snapshots, and storage-level data protection, is handled by other VCF components such as VCF Operations, VCF Log Management, and vSAN Data Protection.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable retention mechanisms that allow administrators to align disaster recovery and cyber recovery data with retention obligations. PNR snapshot schedules define a retention policy that determines how long each snapshot is retained, with hourly, daily, weekly, and monthly cadences and a maximum retention duration of three years. Administrators can also select predefined retention templates that combine recovery point objective (RPO) and snapshot retention parameters for quick configuration of protection groups.
-For vSphere Replication, the retention policy determines the expiration of point-in-time copies, and storage consumption drops after all point-in-time copies referring to the original disk are expired. Administrators configure the number of retention slots and the spacing between recovery points, so older instances expire automatically once the configured limit is exceeded.
-Cyber Recovery snapshot schedules in PNR follow the same retention model, defining a retention policy that controls how long each snapshot is retained. Administrators should account for storage capacity when configuring longer retention schedules, since extended retention periods increase storage consumption on the underlying datastores.
-These retention controls allow organizations to align disaster recovery and cyber recovery data retention with applicable statutory, regulatory, and contractual obligations. PNR provides the technical mechanisms; determining the specific retention durations that satisfy each obligation is an organizational policy decision.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides configurable backup retention controls that support an organization's data retention requirements for its managed databases. These controls do not define retention obligations, which come from the organization's legal and compliance functions, but they provide the technical means to implement those obligations for PostgreSQL, MySQL, SQL Server, and MinIO data.
-Retention periods are configured through Data Service Policies in the DSM administration interface. Each policy supports a backup-retention-period setting that defines the duration for which backups are kept. When multiple policies apply to a namespace, DSM aggregates the retention constraints by selecting the more restrictive minimum and maximum retention day values, producing a resultant retention window that reflects all applicable policies. Data service policies can also be tailored to specific requirements and enforced across different tenants, giving administrators a consistent mechanism for applying retention standards in multi-tenant deployments.
-For deleted databases, DSM retains automated backups according to the configured retention period and exposes an Archives tab in the administration interface where administrators can access and adjust the retention period of retained backups. This allows organizations to maintain access to backup data even after a database instance has been removed, supporting retention obligations that outlast the operational lifetime of a specific database. When a database is deleted, automated backups continue to be retained until the retention policy is met.
-DSM also supports point-in-time restore within the backup retention period, enabling recovery to any point within the retained window. On-demand backups behave differently from automated backups: they are permanent and do not expire automatically. On-demand backups remain in the backup storage location until an administrator manually deletes them, which means they can consume storage quota indefinitely and require separate tracking for retention compliance.
-Data service policies also define backup storage locations (S3-compatible targets) alongside retention duration. If a data service policy that is in use is deleted, the data services associated with that policy become non-compliant, alerting administrators to a configuration gap.
-Meeting this control fully requires the organization to determine the applicable retention periods, communicate those requirements to DSM administrators, and configure policies accordingly. DSM does not automatically derive retention obligations from regulatory or contractual sources. Its retention controls also cover only the database data it manages and do not address retention of all media and data types that may fall within an organization's broader retention obligations.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
